--- a/添順/統計表.xlsx
+++ b/添順/統計表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f225da5f600723a9/桌面/運籌計畫/huaTTT_bus_data_23to25/huaTTT_bus_data_23to25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\添順\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="300" documentId="8_{978E527D-C310-440A-B90D-AEA721DE961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ADAB385-1021-4F9D-A8D0-6020100D9E1C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4102DC8-02C8-416B-BAB8-49AB0D0C52ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{D696006E-6B09-4A1F-B765-609C9920021E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{D696006E-6B09-4A1F-B765-609C9920021E}"/>
   </bookViews>
   <sheets>
     <sheet name="112年至114年台東縣公路客運年總運量統計表" sheetId="1" r:id="rId1"/>
@@ -63,28 +63,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">             年份
-票種</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>學生票</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>無法辨識</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>總計</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>普通票
-(含TPASS)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>113年成長率</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -105,25 +87,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>花蓮縣</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>臺東縣</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>非定期票</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>花蓮縣
-(含花東公路客運)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">                       年份
 定期票</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通
+(含TPASS)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>學生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">             年份
+持卡身分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>無法區別</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺東縣199</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花蓮縣399</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>花蓮縣199</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -136,7 +135,7 @@
     <numFmt numFmtId="176" formatCode="000"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="#,##0_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -261,20 +260,20 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -293,10 +292,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,13 +612,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5495D3-7844-4C62-A36B-CC5FFA174E31}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="7" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="2" max="7" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -640,7 +635,7 @@
       </c>
       <c r="G1" s="11"/>
     </row>
-    <row r="2" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -666,7 +661,7 @@
         <v>0.37803532187438305</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -692,7 +687,7 @@
         <v>0.21760354534872556</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -718,7 +713,7 @@
         <v>0.19048482082849225</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -744,7 +739,7 @@
         <v>0.1732467708997466</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -770,7 +765,7 @@
         <v>4.0629541048652532E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -812,16 +807,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81233597-EACB-469C-BF7E-B035EB2699ED}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="1" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B1" s="2">
         <v>112</v>
@@ -833,15 +828,15 @@
         <v>114</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="9">
         <v>292653</v>
@@ -852,16 +847,16 @@
       <c r="D2" s="9">
         <v>295308</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <f>(C2-B2)/B2</f>
         <v>0.21511141180852408</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <f>(D2-C2)/C2</f>
         <v>-0.16956406809783861</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="5">
         <f>B2/$B$14</f>
@@ -875,12 +870,12 @@
         <f>D2/$D$14</f>
         <v>0.31857650969134621</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" s="9">
         <v>348851</v>
@@ -891,16 +886,16 @@
       <c r="D4" s="9">
         <v>318058</v>
       </c>
-      <c r="E4" s="10">
-        <f t="shared" ref="E4:E15" si="0">(C4-B4)/B4</f>
+      <c r="E4" s="12">
+        <f t="shared" ref="E4" si="0">(C4-B4)/B4</f>
         <v>7.6952624472912498E-2</v>
       </c>
-      <c r="F4" s="10">
-        <f t="shared" ref="F4:F15" si="1">(D4-C4)/C4</f>
+      <c r="F4" s="12">
+        <f t="shared" ref="F4" si="1">(D4-C4)/C4</f>
         <v>-0.15341659213832459</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="5">
         <f>B4/$B$14</f>
@@ -914,12 +909,12 @@
         <f>D4/$D$14</f>
         <v>0.34311907404950154</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" s="9">
         <v>194152</v>
@@ -930,16 +925,16 @@
       <c r="D6" s="9">
         <v>90906</v>
       </c>
-      <c r="E6" s="10">
-        <f t="shared" ref="E6:E15" si="2">(C6-B6)/B6</f>
+      <c r="E6" s="12">
+        <f t="shared" ref="E6" si="2">(C6-B6)/B6</f>
         <v>-0.29264699822819235</v>
       </c>
-      <c r="F6" s="10">
-        <f t="shared" ref="F6:F15" si="3">(D6-C6)/C6</f>
+      <c r="F6" s="12">
+        <f t="shared" ref="F6" si="3">(D6-C6)/C6</f>
         <v>-0.33806632006640747</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="5">
         <f>B6/$B$14</f>
@@ -953,12 +948,12 @@
         <f>D6/$D$14</f>
         <v>9.8068850793075438E-2</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B8" s="9">
         <v>10653</v>
@@ -969,16 +964,16 @@
       <c r="D8" s="9">
         <v>12209</v>
       </c>
-      <c r="E8" s="10">
-        <f t="shared" ref="E8:E15" si="4">(C8-B8)/B8</f>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8" si="4">(C8-B8)/B8</f>
         <v>0.20003754810851404</v>
       </c>
-      <c r="F8" s="10">
-        <f t="shared" ref="F8:F15" si="5">(D8-C8)/C8</f>
+      <c r="F8" s="12">
+        <f t="shared" ref="F8" si="5">(D8-C8)/C8</f>
         <v>-4.4978097622027535E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="5">
         <f>B8/$B$14</f>
@@ -992,12 +987,12 @@
         <f>D8/$D$14</f>
         <v>1.317099640653706E-2</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B10" s="9">
         <v>10162</v>
@@ -1008,16 +1003,16 @@
       <c r="D10" s="9">
         <v>4742</v>
       </c>
-      <c r="E10" s="10">
-        <f t="shared" ref="E10:E15" si="6">(C10-B10)/B10</f>
+      <c r="E10" s="12">
+        <f t="shared" ref="E10" si="6">(C10-B10)/B10</f>
         <v>-0.39883881125762644</v>
       </c>
-      <c r="F10" s="10">
-        <f t="shared" ref="F10:F15" si="7">(D10-C10)/C10</f>
+      <c r="F10" s="12">
+        <f t="shared" ref="F10" si="7">(D10-C10)/C10</f>
         <v>-0.22376821083647078</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="5">
         <f>B10/$B$14</f>
@@ -1031,12 +1026,12 @@
         <f>D10/$D$14</f>
         <v>5.115641326873515E-3</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B12" s="9">
         <v>27028</v>
@@ -1047,16 +1042,16 @@
       <c r="D12" s="9">
         <v>205738</v>
       </c>
-      <c r="E12" s="10">
-        <f t="shared" ref="E12:E15" si="8">(C12-B12)/B12</f>
+      <c r="E12" s="12">
+        <f t="shared" ref="E12" si="8">(C12-B12)/B12</f>
         <v>4.3485644516797395</v>
       </c>
-      <c r="F12" s="10">
-        <f t="shared" ref="F12:F15" si="9">(D12-C12)/C12</f>
+      <c r="F12" s="12">
+        <f t="shared" ref="F12" si="9">(D12-C12)/C12</f>
         <v>0.42319159386003141</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="5">
         <f>B12/$B$14</f>
@@ -1070,12 +1065,12 @@
         <f>D12/$D$14</f>
         <v>0.2219489277326662</v>
       </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" s="9">
         <f>SUM(+B2+B4+B6+B8+B10+B12)</f>
@@ -1089,16 +1084,16 @@
         <f>SUM(+D2+D4+D6+D8+D10+D12)</f>
         <v>926961</v>
       </c>
-      <c r="E14" s="10">
-        <f t="shared" ref="E14:E15" si="10">(C14-B14)/B14</f>
+      <c r="E14" s="12">
+        <f t="shared" ref="E14" si="10">(C14-B14)/B14</f>
         <v>0.16818468385363197</v>
       </c>
-      <c r="F14" s="10">
-        <f t="shared" ref="F14:F15" si="11">(D14-C14)/C14</f>
+      <c r="F14" s="12">
+        <f t="shared" ref="F14" si="11">(D14-C14)/C14</f>
         <v>-0.10186030288056275</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="5">
         <v>1</v>
@@ -1109,24 +1104,17 @@
       <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-    </row>
-    <row r="17" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+    </row>
+    <row r="17" spans="1:1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="E4:E5"/>
@@ -1142,6 +1130,13 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A14:A15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1151,15 +1146,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1B3490-4979-4C12-9191-BD96B78957B8}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="6" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.625" customWidth="1"/>
+    <col min="2" max="6" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2">
         <v>112</v>
@@ -1171,33 +1166,33 @@
         <v>114</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="10">
         <v>0</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="10">
         <v>0</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="5">
         <f>B2/$B$10</f>
@@ -1211,11 +1206,11 @@
         <f>D2/$D$10</f>
         <v>1.0787940377211124E-6</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="9">
@@ -1227,16 +1222,16 @@
       <c r="D4" s="9">
         <v>6353</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="12">
         <f t="shared" ref="E4:F4" si="0">(C4-B4)/B4</f>
         <v>5.1736111111111107</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="12">
         <f t="shared" si="0"/>
         <v>-0.2059742532183477</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="5">
         <f>B4/$B$10</f>
@@ -1250,12 +1245,12 @@
         <f>D4/$D$10</f>
         <v>6.8535785216422267E-3</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="9">
         <v>63991</v>
@@ -1266,16 +1261,16 @@
       <c r="D6" s="9">
         <v>312150</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <f t="shared" ref="E6:F6" si="1">(C6-B6)/B6</f>
         <v>3.3629104092763047</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <f t="shared" si="1"/>
         <v>0.11806781834397734</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="5">
         <f>B6/$B$10</f>
@@ -1289,12 +1284,12 @@
         <f>D6/$D$10</f>
         <v>0.33674555887464519</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B8" s="9">
         <v>818212</v>
@@ -1305,16 +1300,16 @@
       <c r="D8" s="9">
         <v>608457</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="12">
         <f t="shared" ref="E8:F8" si="2">(C8-B8)/B8</f>
         <v>-8.9597805947602818E-2</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <f t="shared" si="2"/>
         <v>-0.18317174608203496</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="5">
         <f>B8/$B$10</f>
@@ -1328,12 +1323,12 @@
         <f>D8/$D$10</f>
         <v>0.65639978380967479</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B10" s="9">
         <f>SUM(+B2+B4+B6+B8)</f>
@@ -1347,16 +1342,16 @@
         <f t="shared" si="3"/>
         <v>926961</v>
       </c>
-      <c r="E10" s="10">
-        <f t="shared" ref="E10:F11" si="4">(C10-B10)/B10</f>
+      <c r="E10" s="12">
+        <f t="shared" ref="E10:F10" si="4">(C10-B10)/B10</f>
         <v>0.16818468385363197</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="12">
         <f t="shared" si="4"/>
         <v>-0.10186030288056275</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="5">
         <v>1</v>
@@ -1367,11 +1362,17 @@
       <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
@@ -1381,12 +1382,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/添順/統計表.xlsx
+++ b/添順/統計表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f225da5f600723a9/桌面/運籌計畫/huaTTT_bus_data_23to25/huaTTT_bus_data_23to25/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\添順\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="8_{978E527D-C310-440A-B90D-AEA721DE961C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25212882-3565-475B-BBA2-8659ECD3E8B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17882592-6583-4EE7-B095-3EB9E771259B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D696006E-6B09-4A1F-B765-609C9920021E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{D696006E-6B09-4A1F-B765-609C9920021E}"/>
   </bookViews>
   <sheets>
     <sheet name="112年至114年台東縣公路客運年總運量統計表" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
     <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="#,##0_ "/>
     <numFmt numFmtId="179" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="180" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="180" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -188,7 +188,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -228,6 +228,32 @@
         <color auto="1"/>
       </diagonal>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -240,7 +266,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -268,25 +294,49 @@
     <xf numFmtId="179" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -306,10 +356,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -629,255 +675,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5495D3-7844-4C62-A36B-CC5FFA174E31}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>17</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="G1" s="11"/>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="12">
         <v>334882</v>
       </c>
-      <c r="C2" s="2">
-        <f>B2/B$7</f>
+      <c r="C2" s="12">
+        <v>450501</v>
+      </c>
+      <c r="D2" s="12">
+        <v>350424</v>
+      </c>
+      <c r="E2" s="18">
+        <f>(C2-B2)/C2</f>
+        <v>0.25664537925553993</v>
+      </c>
+      <c r="F2" s="18">
+        <f>(D2-C2)/D2</f>
+        <v>-0.28558831586877609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="23"/>
+      <c r="B3" s="2">
+        <f>B2/B$12</f>
         <v>0.37584623258152566</v>
       </c>
-      <c r="D2" s="9">
-        <v>450501</v>
-      </c>
-      <c r="E2" s="2">
-        <f>D2/D$7</f>
+      <c r="C3" s="2">
+        <f>C2/C$12</f>
         <v>0.43369488934306683</v>
       </c>
-      <c r="F2" s="9">
-        <v>350424</v>
-      </c>
-      <c r="G2" s="2">
-        <f>F2/F$7</f>
+      <c r="D3" s="2">
+        <f>D2/D$12</f>
         <v>0.37490611940969171</v>
       </c>
-      <c r="H2" s="2">
-        <f>(D2-B2)/D2</f>
-        <v>0.25664537925553993</v>
-      </c>
-      <c r="I2" s="2">
-        <f>(F2-D2)/F2</f>
-        <v>-0.28558831586877609</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+    </row>
+    <row r="4" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B4" s="12">
         <v>202170</v>
       </c>
-      <c r="C3" s="2">
-        <f t="shared" ref="C3:C7" si="0">B3/B$7</f>
+      <c r="C4" s="12">
+        <v>205371</v>
+      </c>
+      <c r="D4" s="12">
+        <v>201710</v>
+      </c>
+      <c r="E4" s="18">
+        <f>(C4-B4)/C4</f>
+        <v>1.5586426515915099E-2</v>
+      </c>
+      <c r="F4" s="18">
+        <f>(D4-C4)/D4</f>
+        <v>-1.8149819047146895E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="23"/>
+      <c r="B5" s="2">
+        <f>B4/B$12</f>
         <v>0.22690031963798304</v>
       </c>
-      <c r="D3" s="9">
-        <v>205371</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" ref="E3:E7" si="1">D3/D$7</f>
+      <c r="C5" s="2">
+        <f>C4/C$12</f>
         <v>0.19770955695830858</v>
       </c>
-      <c r="F3" s="9">
-        <v>201710</v>
-      </c>
-      <c r="G3" s="2">
-        <f t="shared" ref="G3:G7" si="2">F3/F$7</f>
+      <c r="D5" s="2">
+        <f>D4/D$12</f>
         <v>0.21580232331726398</v>
       </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H7" si="3">(D3-B3)/D3</f>
-        <v>1.5586426515915099E-2</v>
-      </c>
-      <c r="I3" s="2">
-        <f t="shared" ref="I3:I7" si="4">(F3-D3)/F3</f>
-        <v>-1.8149819047146895E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+    </row>
+    <row r="6" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B6" s="12">
         <v>17551</v>
       </c>
-      <c r="C4" s="2">
-        <f>B4/B$7</f>
+      <c r="C6" s="12">
+        <v>22626</v>
+      </c>
+      <c r="D6" s="12">
+        <v>18229</v>
+      </c>
+      <c r="E6" s="18">
+        <f>(C6-B6)/C6</f>
+        <v>0.22429947847608944</v>
+      </c>
+      <c r="F6" s="18">
+        <f>(D6-C6)/D6</f>
+        <v>-0.24120906248285698</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23"/>
+      <c r="B7" s="2">
+        <f>B6/B$12</f>
         <v>1.9697915170234163E-2</v>
       </c>
-      <c r="D4" s="9">
-        <v>22626</v>
-      </c>
-      <c r="E4" s="2">
-        <f>D4/D$7</f>
+      <c r="C7" s="2">
+        <f>C6/C$12</f>
         <v>2.1781928489118182E-2</v>
       </c>
-      <c r="F4" s="9">
-        <v>18229</v>
-      </c>
-      <c r="G4" s="2">
-        <f t="shared" si="2"/>
+      <c r="D7" s="2">
+        <f>D6/D$12</f>
         <v>1.9502555905757796E-2</v>
       </c>
-      <c r="H4" s="2">
-        <f t="shared" si="3"/>
-        <v>0.22429947847608944</v>
-      </c>
-      <c r="I4" s="2">
-        <f t="shared" si="4"/>
-        <v>-0.24120906248285698</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+    </row>
+    <row r="8" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B8" s="12">
         <v>137344</v>
       </c>
-      <c r="C5" s="2">
-        <f t="shared" si="0"/>
+      <c r="C8" s="12">
+        <v>149877</v>
+      </c>
+      <c r="D8" s="12">
+        <v>163501</v>
+      </c>
+      <c r="E8" s="18">
+        <f>(C8-B8)/C8</f>
+        <v>8.3621903294034447E-2</v>
+      </c>
+      <c r="F8" s="18">
+        <f>(D8-C8)/D8</f>
+        <v>8.3326707481911427E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23"/>
+      <c r="B9" s="2">
+        <f>B8/B$12</f>
         <v>0.15414451946559402</v>
       </c>
-      <c r="D5" s="9">
-        <v>149877</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="1"/>
+      <c r="C9" s="2">
+        <f>C8/C$12</f>
         <v>0.14428578167433773</v>
       </c>
-      <c r="F5" s="9">
-        <v>163501</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="2"/>
+      <c r="D9" s="2">
+        <f>D8/D$12</f>
         <v>0.17492387915669019</v>
       </c>
-      <c r="H5" s="2">
-        <f t="shared" si="3"/>
-        <v>8.3621903294034447E-2</v>
-      </c>
-      <c r="I5" s="2">
-        <f t="shared" si="4"/>
-        <v>8.3326707481911427E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+    </row>
+    <row r="10" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B10" s="12">
         <v>199061</v>
       </c>
-      <c r="C6" s="2">
-        <f>B6/B$7</f>
+      <c r="C10" s="12">
+        <v>210376</v>
+      </c>
+      <c r="D10" s="12">
+        <v>200834</v>
+      </c>
+      <c r="E10" s="18">
+        <f>(C10-B10)/C10</f>
+        <v>5.3784652241700572E-2</v>
+      </c>
+      <c r="F10" s="18">
+        <f>(D10-C10)/D10</f>
+        <v>-4.7511875479251522E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23"/>
+      <c r="B11" s="2">
+        <f>B10/B$12</f>
         <v>0.22341101314466313</v>
       </c>
-      <c r="D6" s="9">
-        <v>210376</v>
-      </c>
-      <c r="E6" s="2">
-        <f>D6/D$7</f>
+      <c r="C11" s="2">
+        <f>C10/C$12</f>
         <v>0.20252784353516867</v>
       </c>
-      <c r="F6" s="9">
-        <v>200834</v>
-      </c>
-      <c r="G6" s="2">
-        <f t="shared" si="2"/>
+      <c r="D11" s="2">
+        <f>D10/D$12</f>
         <v>0.21486512221059637</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" si="3"/>
-        <v>5.3784652241700572E-2</v>
-      </c>
-      <c r="I6" s="2">
-        <f t="shared" si="4"/>
-        <v>-4.7511875479251522E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+    </row>
+    <row r="12" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="9">
-        <f>B2+B3+B4+B5+B6</f>
+      <c r="B12" s="12">
+        <f>B2+B4+B6+B8+B10</f>
         <v>891008</v>
       </c>
-      <c r="C7" s="2">
-        <f t="shared" ref="C7:G7" si="5">C2+C3+C4+C5+C6</f>
+      <c r="C12" s="12">
+        <f>C2+C4+C6+C8+C10</f>
+        <v>1038751</v>
+      </c>
+      <c r="D12" s="12">
+        <f t="shared" ref="D12" si="0">D2+D4+D6+D8+D10</f>
+        <v>934698</v>
+      </c>
+      <c r="E12" s="20">
+        <f>(C12-B12)/C12</f>
+        <v>0.14223139135365453</v>
+      </c>
+      <c r="F12" s="20">
+        <f>(D12-C12)/D12</f>
+        <v>-0.11132258761653496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="2">
+        <f>B3+B5+B7+B9+B11</f>
         <v>1</v>
       </c>
-      <c r="D7" s="9">
-        <f t="shared" si="5"/>
-        <v>1038751</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="5"/>
+      <c r="C13" s="2">
+        <f>C3+C5+C7+C9+C11</f>
         <v>1</v>
       </c>
-      <c r="F7" s="9">
-        <f t="shared" si="5"/>
-        <v>934698</v>
-      </c>
-      <c r="G7" s="2">
-        <f t="shared" si="5"/>
+      <c r="D13" s="2">
+        <f>D3+D5+D7+D9+D11</f>
         <v>1</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" si="3"/>
-        <v>0.14223139135365453</v>
-      </c>
-      <c r="I7" s="2">
-        <f t="shared" si="4"/>
-        <v>-0.11132258761653496</v>
-      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+  <mergeCells count="18">
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions headings="1"/>
@@ -889,14 +977,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81233597-EACB-469C-BF7E-B035EB2699ED}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="14.88671875" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" customWidth="1"/>
+    <col min="1" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -916,284 +1004,284 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="13">
         <v>296055</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="13">
         <v>358677</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="13">
         <v>298479</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="15">
         <f>(C2-B2)/B2</f>
         <v>0.21152150782793738</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="15">
         <f>(D2-C2)/C2</f>
         <v>-0.16783345461236712</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="9">
         <f>B2/$B$14</f>
         <v>0.33226974393046976</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <f>C2/$C$14</f>
         <v>0.34529641848720244</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="9">
         <f>D2/$D$14</f>
         <v>0.31933201954000118</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="13">
         <v>349263</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="13">
         <v>376016</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="13">
         <v>318542</v>
       </c>
-      <c r="E4" s="13">
-        <f t="shared" ref="E4" si="0">(C4-B4)/B4</f>
+      <c r="E4" s="15">
+        <f>(C4-B4)/B4</f>
         <v>7.6598437280788398E-2</v>
       </c>
-      <c r="F4" s="13">
-        <f t="shared" ref="F4" si="1">(D4-C4)/C4</f>
+      <c r="F4" s="15">
+        <f>(D4-C4)/C4</f>
         <v>-0.15284987872856473</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
+      <c r="B5" s="9">
         <f>B4/$B$14</f>
         <v>0.39198637947134035</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <f>C4/$C$14</f>
         <v>0.36198858051640864</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="9">
         <f>D4/$D$14</f>
         <v>0.34079670652980965</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="13">
         <v>197410</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="13">
         <v>138723</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="13">
         <v>91658</v>
       </c>
-      <c r="E6" s="13">
-        <f t="shared" ref="E6" si="2">(C6-B6)/B6</f>
+      <c r="E6" s="15">
+        <f>(C6-B6)/B6</f>
         <v>-0.29728483866065547</v>
       </c>
-      <c r="F6" s="13">
-        <f t="shared" ref="F6" si="3">(D6-C6)/C6</f>
+      <c r="F6" s="15">
+        <f>(D6-C6)/C6</f>
         <v>-0.33927322794345566</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="9">
         <f>B6/$B$14</f>
         <v>0.22155805559546043</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <f>C6/$C$14</f>
         <v>0.13354788587447811</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="9">
         <f>D6/$D$14</f>
         <v>9.8061619902899119E-2</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="13">
         <v>10653</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="13">
         <v>12785</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="13">
         <v>12212</v>
       </c>
-      <c r="E8" s="13">
-        <f t="shared" ref="E8" si="4">(C8-B8)/B8</f>
+      <c r="E8" s="15">
+        <f t="shared" ref="E8" si="0">(C8-B8)/B8</f>
         <v>0.20013141837979911</v>
       </c>
-      <c r="F8" s="13">
-        <f t="shared" ref="F8" si="5">(D8-C8)/C8</f>
+      <c r="F8" s="15">
+        <f t="shared" ref="F8" si="1">(D8-C8)/C8</f>
         <v>-4.4818146265154478E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="9">
         <f>B8/$B$14</f>
         <v>1.1956121606091078E-2</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="9">
         <f>C8/$C$14</f>
         <v>1.2308050726304956E-2</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="9">
         <f>D8/$D$14</f>
         <v>1.3065182550941587E-2</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="13">
         <v>10165</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="13">
         <v>6111</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="13">
         <v>4742</v>
       </c>
-      <c r="E10" s="13">
-        <f t="shared" ref="E10" si="6">(C10-B10)/B10</f>
+      <c r="E10" s="15">
+        <f t="shared" ref="E10" si="2">(C10-B10)/B10</f>
         <v>-0.39881947860304967</v>
       </c>
-      <c r="F10" s="13">
-        <f t="shared" ref="F10" si="7">(D10-C10)/C10</f>
+      <c r="F10" s="15">
+        <f t="shared" ref="F10" si="3">(D10-C10)/C10</f>
         <v>-0.22402225495009001</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="9">
         <f>B10/$B$14</f>
         <v>1.1408427309294641E-2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="9">
         <f>C10/$C$14</f>
         <v>5.8830268274109969E-3</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="9">
         <f>D10/$D$14</f>
         <v>5.0732964016184908E-3</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="13">
         <v>27462</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="13">
         <v>146439</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="13">
         <v>209065</v>
       </c>
-      <c r="E12" s="13">
-        <f t="shared" ref="E12" si="8">(C12-B12)/B12</f>
+      <c r="E12" s="15">
+        <f t="shared" ref="E12" si="4">(C12-B12)/B12</f>
         <v>4.3324229844876561</v>
       </c>
-      <c r="F12" s="13">
-        <f t="shared" ref="F12" si="9">(D12-C12)/C12</f>
+      <c r="F12" s="15">
+        <f t="shared" ref="F12" si="5">(D12-C12)/C12</f>
         <v>0.42765929841094247</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="17"/>
+      <c r="B13" s="9">
         <f>B12/$B$14</f>
         <v>3.0821272087343771E-2</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="9">
         <f>C12/$C$14</f>
         <v>0.14097603756819488</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="9">
         <f>D12/$D$14</f>
         <v>0.22367117507473003</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="13">
         <f>SUM(+B2+B4+B6+B8+B10+B12)</f>
         <v>891008</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="13">
         <f>SUM(+C2+C4+C6+C8+C10+C12)</f>
         <v>1038751</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="13">
         <f>SUM(+D2+D4+D6+D8+D10+D12)</f>
         <v>934698</v>
       </c>
-      <c r="E14" s="13">
-        <f t="shared" ref="E14" si="10">(C14-B14)/B14</f>
+      <c r="E14" s="15">
+        <f t="shared" ref="E14" si="6">(C14-B14)/B14</f>
         <v>0.16581557067950006</v>
       </c>
-      <c r="F14" s="13">
-        <f t="shared" ref="F14" si="11">(D14-C14)/C14</f>
+      <c r="F14" s="15">
+        <f t="shared" ref="F14" si="7">(D14-C14)/C14</f>
         <v>-0.10017126337303164</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
-      <c r="B15" s="2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="17"/>
+      <c r="B15" s="9">
         <v>1</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="9">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="9">
         <v>1</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-    </row>
-    <row r="17" spans="1:1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+    </row>
+    <row r="17" spans="1:1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1228,13 +1316,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1B3490-4979-4C12-9191-BD96B78957B8}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="6" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.625" customWidth="1"/>
+    <col min="2" max="6" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
@@ -1254,84 +1342,84 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1296</v>
+      </c>
+      <c r="C2" s="6">
+        <v>8001</v>
       </c>
       <c r="D2" s="6">
-        <v>1</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
+        <v>6353</v>
+      </c>
+      <c r="E2" s="15">
+        <f t="shared" ref="E2:F2" si="0">(C2-B2)/B2</f>
+        <v>5.1736111111111107</v>
+      </c>
+      <c r="F2" s="15">
+        <f t="shared" si="0"/>
+        <v>-0.2059742532183477</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
       <c r="B3" s="2">
         <f>B2/$B$10</f>
-        <v>0</v>
+        <v>1.4545323947708663E-3</v>
       </c>
       <c r="C3" s="2">
         <f>C2/$C$10</f>
-        <v>0</v>
+        <v>7.7025196606308926E-3</v>
       </c>
       <c r="D3" s="2">
         <f>D2/$D$10</f>
-        <v>1.0698642770178176E-6</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1296</v>
-      </c>
-      <c r="C4" s="6">
-        <v>8001</v>
+        <v>6.7968477518941944E-3</v>
+      </c>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="7">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
       </c>
       <c r="D4" s="6">
-        <v>6353</v>
-      </c>
-      <c r="E4" s="13">
-        <f t="shared" ref="E4:F4" si="0">(C4-B4)/B4</f>
-        <v>5.1736111111111107</v>
-      </c>
-      <c r="F4" s="13">
-        <f t="shared" si="0"/>
-        <v>-0.2059742532183477</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="15">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
       <c r="B5" s="2">
         <f>B4/$B$10</f>
-        <v>1.4545323947708663E-3</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2">
         <f>C4/$C$10</f>
-        <v>7.7025196606308926E-3</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <f>D4/$D$10</f>
-        <v>6.7968477518941944E-3</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+        <v>1.0698642770178176E-6</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="6">
@@ -1343,17 +1431,17 @@
       <c r="D6" s="6">
         <v>317572</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <f t="shared" ref="E6:F6" si="1">(C6-B6)/B6</f>
         <v>3.340209816984455</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f t="shared" si="1"/>
         <v>0.12060241218939004</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
       <c r="B7" s="2">
         <f>B6/$B$10</f>
         <v>7.3282170305990518E-2</v>
@@ -1366,11 +1454,11 @@
         <f>D6/$D$10</f>
         <v>0.33975893818110237</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="6">
@@ -1382,17 +1470,17 @@
       <c r="D8" s="6">
         <v>610772</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="15">
         <f t="shared" ref="E8:F8" si="2">(C8-B8)/B8</f>
         <v>-9.3473327211835752E-2</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <f t="shared" si="2"/>
         <v>-0.18275627679445941</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
       <c r="B9" s="2">
         <f>B8/$B$10</f>
         <v>0.92526329729923862</v>
@@ -1405,36 +1493,36 @@
         <f>D8/$D$10</f>
         <v>0.65344314420272642</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>SUM(+B2+B4+B6+B8)</f>
+        <f>SUM(+B4+B2+B6+B8)</f>
         <v>891008</v>
       </c>
       <c r="C10" s="6">
-        <f t="shared" ref="C10:D10" si="3">SUM(+C2+C4+C6+C8)</f>
+        <f>SUM(+C4+C2+C6+C8)</f>
         <v>1038751</v>
       </c>
       <c r="D10" s="6">
+        <f>SUM(+D4+D2+D6+D8)</f>
+        <v>934698</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" ref="E10:F10" si="3">(C10-B10)/B10</f>
+        <v>0.16581557067950006</v>
+      </c>
+      <c r="F10" s="15">
         <f t="shared" si="3"/>
-        <v>934698</v>
-      </c>
-      <c r="E10" s="13">
-        <f t="shared" ref="E10:F10" si="4">(C10-B10)/B10</f>
-        <v>0.16581557067950006</v>
-      </c>
-      <c r="F10" s="13">
-        <f t="shared" si="4"/>
         <v>-0.10017126337303164</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
       <c r="B11" s="2">
         <v>1</v>
       </c>
@@ -1444,8 +1532,8 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1458,12 +1546,12 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
